--- a/input/images/tables/additional-uscdi-requirements.xlsx
+++ b/input/images/tables/additional-uscdi-requirements.xlsx
@@ -446,7 +446,7 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Contact Detail</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.telecom</t>
+          <t>US Core Patient Profile-Patient.telecom-1</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A Communication Language</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Patient.communication</t>
+          <t>Patient.telecom</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.communication</t>
+          <t>US Core Patient Profile-Patient.telecom-2</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>An Interpreter Needed Flag</t>
+          <t>Preferred Language</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -502,12 +502,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Patient.extension:interpreterRequired</t>
+          <t>Patient.communication</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.extension:interpreterRequired</t>
+          <t>US Core Patient Profile-Patient.communication</t>
         </is>
       </c>
     </row>
@@ -515,22 +515,22 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>An Interpreter Needed Flag</t>
+          <t>Interpreter Needed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US Core Encounter Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Encounter.extension:interpreterRequired</t>
+          <t>Patient.extension:interpreterRequired</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>US Core Encounter Profile-Encounter.extension:interpreterRequired</t>
+          <t>US Core Patient Profile-Patient.extension:interpreterRequired</t>
         </is>
       </c>
     </row>
@@ -538,45 +538,49 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A Race</t>
+          <t>Interpreter Needed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core Encounter Profile</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patient.extension:race</t>
+          <t>Encounter.extension:interpreterRequired</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.extension:race</t>
+          <t>US Core Encounter Profile-Encounter.extension:interpreterRequired</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>An Ethnicity</t>
+          <t>Appointment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core Encounter Profile</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Patient.extension:ethnicity</t>
+          <t>Encounter.appointment</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.extension:ethnicity</t>
+          <t>US Core Encounter Profile-Encounter.appointment</t>
         </is>
       </c>
     </row>
@@ -584,7 +588,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A Tribal Affiliation</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -594,12 +598,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Patient.extension:tribalAffiliation</t>
+          <t>Patient.extension:race</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.extension:tribalAffiliation</t>
+          <t>US Core Patient Profile-Patient.extension:race</t>
         </is>
       </c>
     </row>
@@ -607,7 +611,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A Sex</t>
+          <t>Ethnicity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,12 +621,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Patient.extension:sex</t>
+          <t>Patient.extension:ethnicity</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.extension:sex</t>
+          <t>US Core Patient Profile-Patient.extension:ethnicity</t>
         </is>
       </c>
     </row>
@@ -630,7 +634,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Date Of Death</t>
+          <t>Tribal Affiliation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -640,12 +644,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Patient.deceased[x]</t>
+          <t>Patient.extension:tribalAffiliation</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.deceased[x]</t>
+          <t>US Core Patient Profile-Patient.extension:tribalAffiliation</t>
         </is>
       </c>
     </row>
@@ -653,7 +657,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Address Use</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -663,12 +667,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Patient.address.use</t>
+          <t>Patient.extension:sex</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.address.use</t>
+          <t>US Core Patient Profile-Patient.extension:sex</t>
         </is>
       </c>
     </row>
@@ -676,7 +680,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Address Period</t>
+          <t>Date of Death</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -686,12 +690,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Patient.address.period</t>
+          <t>Patient.deceased[x]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.address.period</t>
+          <t>US Core Patient Profile-Patient.deceased[x]</t>
         </is>
       </c>
     </row>
@@ -699,7 +703,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Previous Name</t>
+          <t>Previous Address</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -709,12 +713,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Patient.name.use</t>
+          <t>Patient.address.use</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.name.use</t>
+          <t>US Core Patient Profile-Patient.address.use</t>
         </is>
       </c>
     </row>
@@ -722,7 +726,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name Period</t>
+          <t>Previous Address</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,12 +736,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Patient.name.period</t>
+          <t>Patient.address.period</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.name.period</t>
+          <t>US Core Patient Profile-Patient.address.period</t>
         </is>
       </c>
     </row>
@@ -745,7 +749,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Suffix</t>
+          <t>Previous Name</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -755,12 +759,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Patient.name.suffix</t>
+          <t>Patient.name.use</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>US Core Patient Profile-Patient.name.suffix</t>
+          <t>US Core Patient Profile-Patient.name.use</t>
         </is>
       </c>
     </row>
@@ -768,22 +772,22 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A Reason Or Indication For Referral Or Consultation</t>
+          <t>Previous Name</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ServiceRequest.reasonCode</t>
+          <t>Patient.name.period</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile-ServiceRequest.reasonCode</t>
+          <t>US Core Patient Profile-Patient.name.period</t>
         </is>
       </c>
     </row>
@@ -791,22 +795,22 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A Reason Or Indication For Referral Or Consultation</t>
+          <t>Name Suffix</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ServiceRequest.reasonReference</t>
+          <t>Patient.name.suffix</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile-ServiceRequest.reasonReference</t>
+          <t>US Core Patient Profile-Patient.name.suffix</t>
         </is>
       </c>
     </row>
@@ -814,22 +818,22 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A Reason Or Indication For Referral Or Consultation</t>
+          <t>Indication</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile</t>
+          <t>US Core ServiceRequest Profile</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Procedure.performer</t>
+          <t>ServiceRequest.reasonCode</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile-Procedure.performer</t>
+          <t>US Core ServiceRequest Profile-ServiceRequest.reasonCode</t>
         </is>
       </c>
     </row>
@@ -837,22 +841,22 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A Reason Or Indication For Referral Or Consultation</t>
+          <t>Indication</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile</t>
+          <t>US Core ServiceRequest Profile</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Procedure.performer.actor</t>
+          <t>ServiceRequest.reasonReference</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile-Procedure.performer.actor</t>
+          <t>US Core ServiceRequest Profile-ServiceRequest.reasonReference</t>
         </is>
       </c>
     </row>
@@ -860,7 +864,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A Reason Or Indication For Referral Or Consultation</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -870,12 +874,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Procedure.reasonCode</t>
+          <t>Procedure.performer</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile-Procedure.reasonCode</t>
+          <t>US Core Procedure Profile-Procedure.performer</t>
         </is>
       </c>
     </row>
@@ -883,7 +887,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A Reason Or Indication For Referral Or Consultation</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -893,12 +897,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Procedure.reasonReference</t>
+          <t>Procedure.performer.actor</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile-Procedure.reasonReference</t>
+          <t>US Core Procedure Profile-Procedure.performer.actor</t>
         </is>
       </c>
     </row>
@@ -906,22 +910,22 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Reason Or Indication For The Prescription</t>
+          <t>Indication</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile</t>
+          <t>US Core Procedure Profile</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MedicationRequest.reasonCode</t>
+          <t>Procedure.reasonCode</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile-MedicationRequest.reasonCode</t>
+          <t>US Core Procedure Profile-Procedure.reasonCode</t>
         </is>
       </c>
     </row>
@@ -929,22 +933,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Reason Or Indication For The Prescription</t>
+          <t>Indication</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile</t>
+          <t>US Core Procedure Profile</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MedicationRequest.reasonReference</t>
+          <t>Procedure.reasonReference</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile-MedicationRequest.reasonReference</t>
+          <t>US Core Procedure Profile-Procedure.reasonReference</t>
         </is>
       </c>
     </row>
@@ -952,7 +956,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Medication Adherence</t>
+          <t>Indication</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -962,12 +966,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MedicationRequest.extension:medicationAdherence</t>
+          <t>MedicationRequest.reasonCode</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile-MedicationRequest.extension:medicationAdherence</t>
+          <t>US Core MedicationRequest Profile-MedicationRequest.reasonCode</t>
         </is>
       </c>
     </row>
@@ -975,22 +979,22 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A Reference To The Request For The Procedure</t>
+          <t>Indication</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile</t>
+          <t>US Core MedicationRequest Profile</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Procedure.basedOn</t>
+          <t>MedicationRequest.reasonReference</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile-Procedure.basedOn</t>
+          <t>US Core MedicationRequest Profile-MedicationRequest.reasonReference</t>
         </is>
       </c>
     </row>
@@ -998,22 +1002,22 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>US Core Document Category</t>
+          <t>Medication Adherence</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Profile</t>
+          <t>US Core MedicationRequest Profile</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DocumentReference.category:uscore</t>
+          <t>MedicationRequest.extension:medicationAdherence</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Profile-DocumentReference.category:uscore</t>
+          <t>US Core MedicationRequest Profile-MedicationRequest.extension:medicationAdherence</t>
         </is>
       </c>
     </row>
@@ -1021,45 +1025,49 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>References To An Associated Survey, Assessment, Or Screening Tool</t>
+          <t>Reason for Referral</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US Core Simple Observation Profile</t>
+          <t>US Core Procedure Profile</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Observation.derivedFrom</t>
+          <t>Procedure.basedOn</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>US Core Simple Observation Profile-Observation.derivedFrom</t>
+          <t>US Core Procedure Profile-Procedure.basedOn</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Specimen Source Site</t>
+          <t>Reason Not Performed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US Core Specimen Profile</t>
+          <t>US Core Procedure Profile</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Specimen.collection</t>
+          <t>Procedure.extension:recorded</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>US Core Specimen Profile-Specimen.collection</t>
+          <t>US Core Procedure Profile-Procedure.extension:recorded</t>
         </is>
       </c>
     </row>
@@ -1067,22 +1075,22 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Specimen Source Site</t>
+          <t>Clinical Notes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US Core Specimen Profile</t>
+          <t>US Core DocumentReference Profile</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Specimen.collection.bodySite</t>
+          <t>DocumentReference.category:uscore</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>US Core Specimen Profile-Specimen.collection.bodySite</t>
+          <t>US Core DocumentReference Profile-DocumentReference.category:uscore</t>
         </is>
       </c>
     </row>
@@ -1090,22 +1098,22 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Specimen Condition Acceptability</t>
+          <t>Health Status Assessments</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US Core Specimen Profile</t>
+          <t>US Core Simple Observation Profile</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Specimen.condition</t>
+          <t>Observation.derivedFrom</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>US Core Specimen Profile-Specimen.condition</t>
+          <t>US Core Simple Observation Profile-Observation.derivedFrom</t>
         </is>
       </c>
     </row>
@@ -1113,22 +1121,22 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Health Status Assessments</t>
+          <t>Specimen Source Site</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US Core Simple Observation Profile</t>
+          <t>US Core Specimen Profile</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Observation.category:us-core</t>
+          <t>Specimen.collection</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>US Core Simple Observation Profile-Observation.category:us-core</t>
+          <t>US Core Specimen Profile-Specimen.collection</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1144,22 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Health Status Assessments</t>
+          <t>Specimen Source Site</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US Core Observation Screening Assessment Profile</t>
+          <t>US Core Specimen Profile</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Observation.category:screening-assessment</t>
+          <t>Specimen.collection.bodySite</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>US Core Observation Screening Assessment Profile-Observation.category:screening-assessment</t>
+          <t>US Core Specimen Profile-Specimen.collection.bodySite</t>
         </is>
       </c>
     </row>
@@ -1159,68 +1167,76 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Health Status Assessments</t>
+          <t>Specimen Condition</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile</t>
+          <t>US Core Specimen Profile</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Condition.category:screening-assessment</t>
+          <t>Specimen.condition</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile-Condition.category:screening-assessment</t>
+          <t>US Core Specimen Profile-Specimen.condition</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pregnancy Status</t>
+          <t>Specimen Collection Date and Time</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US Core Observation Pregnancy Intent Profile</t>
+          <t>US Core Specimen Profile</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Observation.performer</t>
+          <t>Specimen.collection.collected[x]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>US Core Observation Pregnancy Intent Profile-Observation.performer</t>
+          <t>US Core Specimen Profile-Specimen.collection.collected[x]</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pregnancy Status</t>
+          <t>Specimen Collection Method</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US Core Observation Pregnancy Status Profile</t>
+          <t>US Core Specimen Profile</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Observation.performer</t>
+          <t>Specimen.collection.method</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>US Core Observation Pregnancy Status Profile-Observation.performer</t>
+          <t>US Core Specimen Profile-Specimen.collection.method</t>
         </is>
       </c>
     </row>
@@ -1228,22 +1244,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Provenance Author</t>
+          <t>Health Status Assessments</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US Core AllergyIntolerance Profile</t>
+          <t>US Core Simple Observation Profile</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AllergyIntolerance.recorder</t>
+          <t>Observation.category:us-core</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>US Core AllergyIntolerance Profile-AllergyIntolerance.recorder</t>
+          <t>US Core Simple Observation Profile-Observation.category:us-core</t>
         </is>
       </c>
     </row>
@@ -1251,22 +1267,22 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Provenance Author</t>
+          <t>Health Status Assessments</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US Core Care Experience Preference Profile</t>
+          <t>US Core Observation Screening Assessment Profile</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Observation.performer</t>
+          <t>Observation.category:screening-assessment</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>US Core Care Experience Preference Profile-Observation.performer</t>
+          <t>US Core Observation Screening Assessment Profile-Observation.category:screening-assessment</t>
         </is>
       </c>
     </row>
@@ -1274,22 +1290,22 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Provenance Author</t>
+          <t>Health Status Assessments</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US Core CarePlan Profile</t>
+          <t>US Core Condition Problems and Health Concerns Profile</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CarePlan.contributor</t>
+          <t>Condition.category:screening-assessment</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>US Core CarePlan Profile-CarePlan.contributor</t>
+          <t>US Core Condition Problems and Health Concerns Profile-Condition.category:screening-assessment</t>
         </is>
       </c>
     </row>
@@ -1297,22 +1313,22 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Provenance Author</t>
+          <t>Pregnancy Status</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US Core Condition Encounter Diagnosis Profile</t>
+          <t>US Core Observation Pregnancy Intent Profile</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Condition.recorder</t>
+          <t>Observation.performer</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>US Core Condition Encounter Diagnosis Profile-Condition.recorder</t>
+          <t>US Core Observation Pregnancy Intent Profile-Observation.performer</t>
         </is>
       </c>
     </row>
@@ -1320,45 +1336,49 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Provenance Author</t>
+          <t>Pregnancy Status</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile</t>
+          <t>US Core Observation Pregnancy Status Profile</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Condition.recorder</t>
+          <t>Observation.performer</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile-Condition.recorder</t>
+          <t>US Core Observation Pregnancy Status Profile-Observation.performer</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Provenance Author</t>
+          <t>Allergy Intolerance Criticality</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US Core Observation Occupation Profile</t>
+          <t>US Core AllergyIntolerance Profile</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Observation.performer</t>
+          <t>AllergyIntolerance.criticality</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>US Core Observation Occupation Profile-Observation.performer</t>
+          <t>US Core AllergyIntolerance Profile-AllergyIntolerance.criticality</t>
         </is>
       </c>
     </row>
@@ -1366,22 +1386,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Provenance Author</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US Core Treatment Intervention Preference Profile</t>
+          <t>US Core AllergyIntolerance Profile</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Observation.performer</t>
+          <t>AllergyIntolerance.recorder</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>US Core Treatment Intervention Preference Profile-Observation.performer</t>
+          <t>US Core AllergyIntolerance Profile-AllergyIntolerance.recorder</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1409,22 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile</t>
+          <t>US Core Care Experience Preference Profile</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ServiceRequest.code.text</t>
+          <t>Observation.performer</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile-ServiceRequest.code.text</t>
+          <t>US Core Care Experience Preference Profile-Observation.performer</t>
         </is>
       </c>
     </row>
@@ -1412,22 +1432,22 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Laboratory Tests</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US Core Laboratory Result Observation Profile</t>
+          <t>US Core CarePlan Profile</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Observation.code.text</t>
+          <t>CarePlan.contributor</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>US Core Laboratory Result Observation Profile-Observation.code.text</t>
+          <t>US Core CarePlan Profile-CarePlan.contributor</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1455,22 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Care Plan</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US Core CarePlan Profile</t>
+          <t>US Core Condition Encounter Diagnosis Profile</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CarePlan.addresses</t>
+          <t>Condition.recorder</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>US Core CarePlan Profile-CarePlan.addresses</t>
+          <t>US Core Condition Encounter Diagnosis Profile-Condition.recorder</t>
         </is>
       </c>
     </row>
@@ -1458,22 +1478,22 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Family Health History</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US Core FamilyMemberHistory Profile</t>
+          <t>US Core Condition Problems and Health Concerns Profile</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FamilyMemberHistory.extension:recorder</t>
+          <t>Condition.recorder</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>US Core FamilyMemberHistory Profile-FamilyMemberHistory.extension:recorder</t>
+          <t>US Core Condition Problems and Health Concerns Profile-Condition.recorder</t>
         </is>
       </c>
     </row>
@@ -1481,22 +1501,22 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Unique Device Identifier</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US Core Device Profile</t>
+          <t>US Core Observation Occupation Profile</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Device.udiCarrier</t>
+          <t>Observation.performer</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>US Core Device Profile-Device.udiCarrier</t>
+          <t>US Core Observation Occupation Profile-Observation.performer</t>
         </is>
       </c>
     </row>
@@ -1504,22 +1524,22 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Unique Device Identifier</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US Core Device Profile</t>
+          <t>US Core Treatment Intervention Preference Profile</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Device.distinctIdentifier</t>
+          <t>Observation.performer</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>US Core Device Profile-Device.distinctIdentifier</t>
+          <t>US Core Treatment Intervention Preference Profile-Observation.performer</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1547,22 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Unique Device Identifier</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US Core Device Profile</t>
+          <t>US Core ServiceRequest Profile</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Device.manufactureDate</t>
+          <t>ServiceRequest.code.text</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>US Core Device Profile-Device.manufactureDate</t>
+          <t>US Core ServiceRequest Profile-ServiceRequest.code.text</t>
         </is>
       </c>
     </row>
@@ -1550,22 +1570,22 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Unique Device Identifier</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US Core Device Profile</t>
+          <t>US Core Laboratory Result Observation Profile</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Device.expirationDate</t>
+          <t>Observation.code.text</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>US Core Device Profile-Device.expirationDate</t>
+          <t>US Core Laboratory Result Observation Profile-Observation.code.text</t>
         </is>
       </c>
     </row>
@@ -1573,22 +1593,22 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Unique Device Identifier</t>
+          <t>Care Plan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US Core Device Profile</t>
+          <t>US Core CarePlan Profile</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Device.lotNumber</t>
+          <t>CarePlan.addresses</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>US Core Device Profile-Device.lotNumber</t>
+          <t>US Core CarePlan Profile-CarePlan.addresses</t>
         </is>
       </c>
     </row>
@@ -1596,22 +1616,187 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
+          <t>Family Health History</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>US Core FamilyMemberHistory Profile</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FamilyMemberHistory.extension:recorder</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>US Core FamilyMemberHistory Profile-FamilyMemberHistory.extension:recorder</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>Unique Device Identifier</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>US Core Device Profile</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Device.udiCarrier</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>US Core Device Profile-Device.udiCarrier</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unique Device Identifier</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>US Core Device Profile</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Device.distinctIdentifier</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>US Core Device Profile-Device.distinctIdentifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unique Device Identifier</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>US Core Device Profile</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Device.manufactureDate</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>US Core Device Profile-Device.manufactureDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unique Device Identifier</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>US Core Device Profile</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Device.expirationDate</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>US Core Device Profile-Device.expirationDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unique Device Identifier</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>US Core Device Profile</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Device.lotNumber</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>US Core Device Profile-Device.lotNumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unique Device Identifier</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>US Core Device Profile</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>Device.serialNumber</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>US Core Device Profile-Device.serialNumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Nutrition Order</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>US Core NutritionOrder Profile</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NutritionOrder.oralDiet.instruction</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>US Core NutritionOrder Profile-NutritionOrder.oralDiet.instruction</t>
         </is>
       </c>
     </row>
